--- a/quiz/updated-drill-questions/DRT3.xlsx
+++ b/quiz/updated-drill-questions/DRT3.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25128"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\_5 QUESTION DATABASE\_1 Access Database\Driller's\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\firebrigade\wp-content\plugins\techiquiz\quiz\updated-drill-questions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14EF7A14-10AA-4785-B8C7-2E37844A7083}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E65CD055-9DF3-4123-8ACC-0317D5308DC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4D83A3EA-7D31-4E83-9E35-E9B1B217FB2C}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4D83A3EA-7D31-4E83-9E35-E9B1B217FB2C}"/>
   </bookViews>
   <sheets>
     <sheet name="DRT3" sheetId="1" r:id="rId1"/>
@@ -1161,9 +1161,6 @@
     <t>Start over</t>
   </si>
   <si>
-    <t>Driller's Day 3 Practice Test</t>
-  </si>
-  <si>
     <t>DRT3.1</t>
   </si>
   <si>
@@ -1372,6 +1369,9 @@
   </si>
   <si>
     <t>DRT3.70</t>
+  </si>
+  <si>
+    <t>Driller's Day 3 Practice Test Questions</t>
   </si>
 </sst>
 </file>
@@ -1809,7 +1809,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>378</v>
+        <v>448</v>
       </c>
       <c r="G1" s="4" t="s">
         <v>5</v>
@@ -1841,7 +1841,7 @@
         <v>10</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="F2" s="8" t="s">
         <v>61</v>
@@ -1876,7 +1876,7 @@
         <v>13</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="F3" s="8" t="s">
         <v>65</v>
@@ -1912,7 +1912,7 @@
         <v>13</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="F4" s="8" t="s">
         <v>69</v>
@@ -1947,7 +1947,7 @@
         <v>13</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="F5" s="8" t="s">
         <v>74</v>
@@ -1982,7 +1982,7 @@
         <v>16</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="F6" s="8" t="s">
         <v>79</v>
@@ -2017,7 +2017,7 @@
         <v>16</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="F7" s="8" t="s">
         <v>81</v>
@@ -2052,7 +2052,7 @@
         <v>16</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="F8" s="8" t="s">
         <v>82</v>
@@ -2087,7 +2087,7 @@
         <v>23</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="F9" s="8" t="s">
         <v>87</v>
@@ -2122,7 +2122,7 @@
         <v>24</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="F10" s="8" t="s">
         <v>91</v>
@@ -2157,7 +2157,7 @@
         <v>24</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="F11" s="8" t="s">
         <v>96</v>
@@ -2192,7 +2192,7 @@
         <v>25</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="F12" s="8" t="s">
         <v>101</v>
@@ -2227,7 +2227,7 @@
         <v>25</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="F13" s="8" t="s">
         <v>106</v>
@@ -2262,7 +2262,7 @@
         <v>14</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="F14" s="8" t="s">
         <v>110</v>
@@ -2297,7 +2297,7 @@
         <v>14</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="F15" s="8" t="s">
         <v>114</v>
@@ -2332,7 +2332,7 @@
         <v>27</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="F16" s="8" t="s">
         <v>119</v>
@@ -2367,7 +2367,7 @@
         <v>27</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="F17" s="8" t="s">
         <v>124</v>
@@ -2402,7 +2402,7 @@
         <v>31</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="F18" s="8" t="s">
         <v>129</v>
@@ -2437,7 +2437,7 @@
         <v>32</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="F19" s="8" t="s">
         <v>133</v>
@@ -2472,7 +2472,7 @@
         <v>32</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="F20" s="8" t="s">
         <v>138</v>
@@ -2507,7 +2507,7 @@
         <v>33</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="F21" s="8" t="s">
         <v>143</v>
@@ -2542,7 +2542,7 @@
         <v>34</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="F22" s="8" t="s">
         <v>148</v>
@@ -2577,7 +2577,7 @@
         <v>34</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="F23" s="8" t="s">
         <v>153</v>
@@ -2612,7 +2612,7 @@
         <v>35</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="F24" s="8" t="s">
         <v>158</v>
@@ -2647,7 +2647,7 @@
         <v>35</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="F25" s="8" t="s">
         <v>163</v>
@@ -2682,7 +2682,7 @@
         <v>35</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="F26" s="8" t="s">
         <v>168</v>
@@ -2717,7 +2717,7 @@
         <v>35</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="F27" s="8" t="s">
         <v>172</v>
@@ -2752,7 +2752,7 @@
         <v>35</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="F28" s="8" t="s">
         <v>176</v>
@@ -2787,7 +2787,7 @@
         <v>35</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="F29" s="8" t="s">
         <v>181</v>
@@ -2822,7 +2822,7 @@
         <v>35</v>
       </c>
       <c r="E30" s="7" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="F30" s="8" t="s">
         <v>186</v>
@@ -2857,7 +2857,7 @@
         <v>35</v>
       </c>
       <c r="E31" s="7" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="F31" s="8" t="s">
         <v>191</v>
@@ -2892,7 +2892,7 @@
         <v>35</v>
       </c>
       <c r="E32" s="7" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="F32" s="8" t="s">
         <v>192</v>
@@ -2927,7 +2927,7 @@
         <v>35</v>
       </c>
       <c r="E33" s="7" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="F33" s="8" t="s">
         <v>197</v>
@@ -2962,7 +2962,7 @@
         <v>35</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="F34" s="8" t="s">
         <v>202</v>
@@ -2997,7 +2997,7 @@
         <v>35</v>
       </c>
       <c r="E35" s="7" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="F35" s="8" t="s">
         <v>206</v>
@@ -3032,7 +3032,7 @@
         <v>35</v>
       </c>
       <c r="E36" s="7" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="F36" s="8" t="s">
         <v>210</v>
@@ -3067,7 +3067,7 @@
         <v>42</v>
       </c>
       <c r="E37" s="7" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="F37" s="8" t="s">
         <v>215</v>
@@ -3102,7 +3102,7 @@
         <v>42</v>
       </c>
       <c r="E38" s="7" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="F38" s="8" t="s">
         <v>220</v>
@@ -3137,7 +3137,7 @@
         <v>42</v>
       </c>
       <c r="E39" s="7" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="F39" s="8" t="s">
         <v>223</v>
@@ -3172,7 +3172,7 @@
         <v>42</v>
       </c>
       <c r="E40" s="7" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="F40" s="8" t="s">
         <v>226</v>
@@ -3208,7 +3208,7 @@
         <v>42</v>
       </c>
       <c r="E41" s="7" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="F41" s="8" t="s">
         <v>231</v>
@@ -3244,7 +3244,7 @@
         <v>42</v>
       </c>
       <c r="E42" s="7" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="F42" s="8" t="s">
         <v>236</v>
@@ -3279,7 +3279,7 @@
         <v>43</v>
       </c>
       <c r="E43" s="7" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="F43" s="8" t="s">
         <v>240</v>
@@ -3314,7 +3314,7 @@
         <v>43</v>
       </c>
       <c r="E44" s="7" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F44" s="8" t="s">
         <v>244</v>
@@ -3349,7 +3349,7 @@
         <v>43</v>
       </c>
       <c r="E45" s="7" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="F45" s="8" t="s">
         <v>249</v>
@@ -3384,7 +3384,7 @@
         <v>43</v>
       </c>
       <c r="E46" s="7" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="F46" s="8" t="s">
         <v>254</v>
@@ -3419,7 +3419,7 @@
         <v>45</v>
       </c>
       <c r="E47" s="7" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="F47" s="8" t="s">
         <v>259</v>
@@ -3454,7 +3454,7 @@
         <v>45</v>
       </c>
       <c r="E48" s="7" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="F48" s="8" t="s">
         <v>263</v>
@@ -3489,7 +3489,7 @@
         <v>45</v>
       </c>
       <c r="E49" s="7" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="F49" s="8" t="s">
         <v>268</v>
@@ -3524,7 +3524,7 @@
         <v>45</v>
       </c>
       <c r="E50" s="7" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="F50" s="8" t="s">
         <v>272</v>
@@ -3559,7 +3559,7 @@
         <v>45</v>
       </c>
       <c r="E51" s="7" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="F51" s="8" t="s">
         <v>277</v>
@@ -3594,7 +3594,7 @@
         <v>45</v>
       </c>
       <c r="E52" s="7" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="F52" s="8" t="s">
         <v>280</v>
@@ -3629,7 +3629,7 @@
         <v>45</v>
       </c>
       <c r="E53" s="7" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="F53" s="8" t="s">
         <v>285</v>
@@ -3664,7 +3664,7 @@
         <v>45</v>
       </c>
       <c r="E54" s="7" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="F54" s="8" t="s">
         <v>289</v>
@@ -3699,7 +3699,7 @@
         <v>49</v>
       </c>
       <c r="E55" s="7" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="F55" s="8" t="s">
         <v>294</v>
@@ -3734,7 +3734,7 @@
         <v>49</v>
       </c>
       <c r="E56" s="7" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="F56" s="8" t="s">
         <v>299</v>
@@ -3769,7 +3769,7 @@
         <v>50</v>
       </c>
       <c r="E57" s="7" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="F57" s="8" t="s">
         <v>304</v>
@@ -3804,7 +3804,7 @@
         <v>50</v>
       </c>
       <c r="E58" s="7" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="F58" s="8" t="s">
         <v>309</v>
@@ -3839,7 +3839,7 @@
         <v>50</v>
       </c>
       <c r="E59" s="7" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="F59" s="8" t="s">
         <v>314</v>
@@ -3874,7 +3874,7 @@
         <v>52</v>
       </c>
       <c r="E60" s="7" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="F60" s="8" t="s">
         <v>319</v>
@@ -3909,7 +3909,7 @@
         <v>52</v>
       </c>
       <c r="E61" s="7" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="F61" s="8" t="s">
         <v>324</v>
@@ -3944,7 +3944,7 @@
         <v>52</v>
       </c>
       <c r="E62" s="7" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="F62" s="8" t="s">
         <v>329</v>
@@ -3979,7 +3979,7 @@
         <v>53</v>
       </c>
       <c r="E63" s="7" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F63" s="8" t="s">
         <v>334</v>
@@ -4014,7 +4014,7 @@
         <v>54</v>
       </c>
       <c r="E64" s="7" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="F64" s="8" t="s">
         <v>339</v>
@@ -4049,7 +4049,7 @@
         <v>55</v>
       </c>
       <c r="E65" s="7" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="F65" s="8" t="s">
         <v>344</v>
@@ -4084,7 +4084,7 @@
         <v>55</v>
       </c>
       <c r="E66" s="7" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="F66" s="8" t="s">
         <v>349</v>
@@ -4119,7 +4119,7 @@
         <v>56</v>
       </c>
       <c r="E67" s="7" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="F67" s="8" t="s">
         <v>354</v>
@@ -4154,7 +4154,7 @@
         <v>57</v>
       </c>
       <c r="E68" s="7" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="F68" s="8" t="s">
         <v>359</v>
@@ -4189,7 +4189,7 @@
         <v>57</v>
       </c>
       <c r="E69" s="7" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="F69" s="8" t="s">
         <v>364</v>
@@ -4224,7 +4224,7 @@
         <v>59</v>
       </c>
       <c r="E70" s="7" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="F70" s="8" t="s">
         <v>368</v>
@@ -4259,7 +4259,7 @@
         <v>60</v>
       </c>
       <c r="E71" s="7" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="F71" s="8" t="s">
         <v>373</v>
